--- a/Thesis Forecasting/PAPER CONTEXT/tables/picture_tables/P007_all_plants_actual_vs_benchmark_testing.xlsx
+++ b/Thesis Forecasting/PAPER CONTEXT/tables/picture_tables/P007_all_plants_actual_vs_benchmark_testing.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/benchmark_actual_testing_plots/all_plants_actual_vs_benchmark_testing.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/benchmark_actual_testing_plots/all_plants_actual_vs_benchmark_testing.png</t>
         </is>
       </c>
     </row>
